--- a/src/lib/assets/data/004FELI-02_database.xlsx
+++ b/src/lib/assets/data/004FELI-02_database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jas/Documents/01_Uni/Doktorat/Dissertation/Datenanalyse/analysis_tables/01_Databank_tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Videos\TiT-visualizations\src\lib\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED719E4E-7356-D14E-80E8-A68017B8BC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A59B11-778F-4E6F-8A6C-DA43CDB8092B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="68800" windowHeight="27060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="330" windowWidth="24195" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Messages" sheetId="1" r:id="rId1"/>
@@ -746,7 +746,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -759,7 +759,7 @@
     <col min="12" max="12" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -797,7 +797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -845,7 +845,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -896,7 +896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -998,7 +998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>76</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>25</v>
       </c>
       <c r="C32">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
         <v>64</v>
@@ -2334,7 +2334,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>83</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>83</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>89</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>89</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>95</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>98</v>
       </c>
@@ -3085,12 +3085,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>67</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>95</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>45258</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>98</v>
       </c>
